--- a/tests/fixtures/22_weekly_timesheet/22_weekly_timesheet_pattern-manual.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/22_weekly_timesheet_pattern-manual.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="113">
   <si>
     <t xml:space="preserve">config:</t>
   </si>
@@ -290,6 +290,9 @@
     <t xml:space="preserve">employee.manager</t>
   </si>
   <si>
+    <t xml:space="preserve">var:not-empty</t>
+  </si>
+  <si>
     <t xml:space="preserve">timesheet.week_starting</t>
   </si>
   <si>
@@ -353,40 +356,202 @@
     <t xml:space="preserve">weekTotal.vacationTime</t>
   </si>
   <si>
-    <t xml:space="preserve">rate.regular</t>
+    <t xml:space="preserve">employee.rate.regular</t>
   </si>
   <si>
     <t xml:space="preserve">currency</t>
   </si>
   <si>
-    <t xml:space="preserve">rate.overtime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rate.sick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rate.holiday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rate.vacation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay.regular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay.overtime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay.sick</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay.holiday</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay.vacation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pay.grand_total</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rate.overtime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rate.sick</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rate.holiday</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">rate.vacation</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.pay.regular</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pay.overtime</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pay.sick</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pay.holiday</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pay.vacation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">employee.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">pay.grand_total</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">START:</t>
@@ -449,40 +614,22 @@
     <t xml:space="preserve">FOOTER:1</t>
   </si>
   <si>
-    <t xml:space="preserve">seek:a29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:H30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:I30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:J30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:K30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:L30</t>
+    <t xml:space="preserve">seek:g30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell:next</t>
   </si>
   <si>
     <t xml:space="preserve">cell:H31</t>
   </si>
   <si>
-    <t xml:space="preserve">cell:I31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:J31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:K31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:L31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:K33</t>
+    <t xml:space="preserve">CELL:next</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CeLL:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cElL:next</t>
   </si>
   <si>
     <t xml:space="preserve">END:</t>
@@ -615,7 +762,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -637,6 +784,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1575,17 +1726,15 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>42</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="D32" s="5"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -1598,13 +1747,13 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -1622,10 +1771,10 @@
         <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -1643,10 +1792,10 @@
         <v>44</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1664,10 +1813,10 @@
         <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -1685,10 +1834,10 @@
         <v>40</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -1706,10 +1855,10 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -1727,10 +1876,10 @@
         <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -1748,10 +1897,10 @@
         <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1769,10 +1918,10 @@
         <v>44</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -1790,10 +1939,10 @@
         <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -1808,13 +1957,13 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -1829,13 +1978,13 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -1850,13 +1999,13 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -1871,13 +2020,13 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -1892,13 +2041,13 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -1913,13 +2062,13 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -1932,15 +2081,15 @@
       <c r="L48" s="5"/>
       <c r="M48" s="5"/>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -1953,15 +2102,15 @@
       <c r="L49" s="5"/>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>76</v>
+        <v>55</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -1974,15 +2123,15 @@
       <c r="L50" s="5"/>
       <c r="M50" s="5"/>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>77</v>
+        <v>55</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -1995,15 +2144,15 @@
       <c r="L51" s="5"/>
       <c r="M51" s="5"/>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>78</v>
+        <v>55</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -2018,13 +2167,13 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2037,15 +2186,15 @@
       <c r="L53" s="5"/>
       <c r="M53" s="5"/>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>80</v>
+        <v>55</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2058,15 +2207,15 @@
       <c r="L54" s="5"/>
       <c r="M54" s="5"/>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>81</v>
+        <v>55</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2079,15 +2228,15 @@
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>82</v>
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2100,15 +2249,15 @@
       <c r="L56" s="5"/>
       <c r="M56" s="5"/>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>83</v>
+        <v>55</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2121,15 +2270,15 @@
       <c r="L57" s="5"/>
       <c r="M57" s="5"/>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>84</v>
+        <v>55</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -2143,417 +2292,417 @@
       <c r="M58" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
+      <c r="A60" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="7"/>
+      <c r="H60" s="7"/>
+      <c r="I60" s="7"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61" s="7" t="s">
+      <c r="A61" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
+      <c r="B61" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="M61" s="8"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="B62" s="8" t="s">
+      <c r="A62" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B62" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8"/>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="8"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+      <c r="M62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="B63" s="8" t="s">
+      <c r="A63" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B63" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
-      <c r="M63" s="8"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+      <c r="M63" s="9"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B64" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="7"/>
-      <c r="H64" s="7"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
+      <c r="A64" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="M64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
-      <c r="M65" s="8"/>
+      <c r="A65" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+      <c r="M65" s="9"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B66" s="8" t="s">
+      <c r="A66" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8"/>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="8"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+      <c r="M66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B67" s="8" t="s">
+      <c r="A67" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B67" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8"/>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
-      <c r="M67" s="8"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+      <c r="M67" s="9"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B68" s="8" t="s">
+      <c r="A68" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B68" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8"/>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="8"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B69" s="8" t="s">
+      <c r="A69" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B69" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8"/>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
-      <c r="M69" s="8"/>
+      <c r="C69" s="9"/>
+      <c r="D69" s="9"/>
+      <c r="E69" s="9"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
+      <c r="I69" s="9"/>
+      <c r="J69" s="9"/>
+      <c r="K69" s="9"/>
+      <c r="L69" s="9"/>
+      <c r="M69" s="9"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B70" s="7" t="s">
+      <c r="A70" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="M70" s="8"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="9"/>
+      <c r="I71" s="9"/>
+      <c r="J71" s="9"/>
+      <c r="K71" s="9"/>
+      <c r="L71" s="9"/>
+      <c r="M71" s="9"/>
+    </row>
+    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="9"/>
+      <c r="H72" s="9"/>
+      <c r="I72" s="9"/>
+      <c r="J72" s="9"/>
+      <c r="K72" s="9"/>
+      <c r="L72" s="9"/>
+      <c r="M72" s="9"/>
+    </row>
+    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
         <v>94</v>
-      </c>
-      <c r="C70" s="7"/>
-      <c r="D70" s="7"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="7"/>
-      <c r="H70" s="7"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="7"/>
-      <c r="K70" s="7"/>
-      <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
-    </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8"/>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
-      <c r="M71" s="8"/>
-    </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="8"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="s">
-        <v>93</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
-      <c r="M73" s="8"/>
+      <c r="C73" s="9"/>
+      <c r="D73" s="9"/>
+      <c r="E73" s="9"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="9"/>
+      <c r="H73" s="9"/>
+      <c r="I73" s="9"/>
+      <c r="J73" s="9"/>
+      <c r="K73" s="9"/>
+      <c r="L73" s="9"/>
+      <c r="M73" s="9"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B74" s="8" t="s">
+      <c r="A74" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B74" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="8"/>
+      <c r="C74" s="9"/>
+      <c r="D74" s="9"/>
+      <c r="E74" s="9"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="9"/>
+      <c r="H74" s="9"/>
+      <c r="I74" s="9"/>
+      <c r="J74" s="9"/>
+      <c r="K74" s="9"/>
+      <c r="L74" s="9"/>
+      <c r="M74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="8" t="s">
-        <v>93</v>
+      <c r="A75" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
-      <c r="M75" s="8"/>
+      <c r="C75" s="9"/>
+      <c r="D75" s="9"/>
+      <c r="E75" s="9"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+      <c r="J75" s="9"/>
+      <c r="K75" s="9"/>
+      <c r="L75" s="9"/>
+      <c r="M75" s="9"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B76" s="8" t="s">
+      <c r="A76" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B76" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8"/>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="8"/>
+      <c r="C76" s="9"/>
+      <c r="D76" s="9"/>
+      <c r="E76" s="9"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76" s="9"/>
+      <c r="K76" s="9"/>
+      <c r="L76" s="9"/>
+      <c r="M76" s="9"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="8" t="s">
-        <v>93</v>
+      <c r="A77" s="9" t="s">
+        <v>94</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8"/>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
-      <c r="M77" s="8"/>
+      <c r="C77" s="9"/>
+      <c r="D77" s="9"/>
+      <c r="E77" s="9"/>
+      <c r="F77" s="9"/>
+      <c r="G77" s="9"/>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9"/>
+      <c r="L77" s="9"/>
+      <c r="M77" s="9"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="B78" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8"/>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
-      <c r="M78" s="8"/>
+      <c r="A78" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" s="9"/>
+      <c r="D78" s="9"/>
+      <c r="E78" s="9"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
+      <c r="K78" s="9"/>
+      <c r="L78" s="9"/>
+      <c r="M78" s="9"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8"/>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
-      <c r="M79" s="8"/>
+      <c r="A79" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B79" s="9"/>
+      <c r="C79" s="9"/>
+      <c r="D79" s="9"/>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="9"/>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
+      <c r="K79" s="9"/>
+      <c r="L79" s="9"/>
+      <c r="M79" s="9"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B80" s="9"/>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9"/>
-      <c r="F80" s="9"/>
-      <c r="G80" s="9"/>
-      <c r="H80" s="9"/>
-      <c r="I80" s="9"/>
-      <c r="J80" s="9"/>
-      <c r="K80" s="9"/>
-      <c r="L80" s="9"/>
-      <c r="M80" s="9"/>
+      <c r="A80" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B80" s="10"/>
+      <c r="C80" s="10"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="10"/>
+      <c r="H80" s="10"/>
+      <c r="I80" s="10"/>
+      <c r="J80" s="10"/>
+      <c r="K80" s="10"/>
+      <c r="L80" s="10"/>
+      <c r="M80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="9"/>
-      <c r="B81" s="9" t="s">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="C81" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D81" s="9" t="s">
+      <c r="D81" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="9"/>
-      <c r="G81" s="9"/>
-      <c r="H81" s="9"/>
-      <c r="I81" s="9"/>
-      <c r="J81" s="9"/>
-      <c r="K81" s="9"/>
-      <c r="L81" s="9"/>
-      <c r="M81" s="9"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="10"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="10"/>
+      <c r="K81" s="10"/>
+      <c r="L81" s="10"/>
+      <c r="M81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>22</v>
@@ -2565,10 +2714,10 @@
         <v>26</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>28</v>
@@ -2590,364 +2739,364 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="10"/>
-      <c r="B83" s="10" t="s">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D83" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="F83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="I83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="K83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L83" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="M83" s="10" t="s">
-        <v>100</v>
+      <c r="E83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="H83" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="L83" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="M83" s="11" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L84" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="M90" s="8"/>
+      <c r="A90" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B90" s="9"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9"/>
+      <c r="G90" s="9"/>
+      <c r="H90" s="9"/>
+      <c r="I90" s="9"/>
+      <c r="J90" s="9"/>
+      <c r="K90" s="9"/>
+      <c r="L90" s="9"/>
+      <c r="M90" s="9"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="8"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="M91" s="8"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="8" t="s">
+      <c r="A91" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="B92" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="8"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="M92" s="8"/>
-    </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="8" t="s">
+      <c r="B91" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9"/>
+      <c r="G91" s="9"/>
+      <c r="H91" s="9"/>
+      <c r="I91" s="9"/>
+      <c r="J91" s="9"/>
+      <c r="K91" s="9"/>
+      <c r="L91" s="9"/>
+      <c r="M91" s="9"/>
+    </row>
+    <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="9"/>
+      <c r="I92" s="9"/>
+      <c r="J92" s="9"/>
+      <c r="K92" s="9"/>
+      <c r="L92" s="9"/>
+      <c r="M92" s="9"/>
+    </row>
+    <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9"/>
+      <c r="G93" s="9"/>
+      <c r="H93" s="9"/>
+      <c r="I93" s="9"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="9"/>
+      <c r="L93" s="9"/>
+      <c r="M93" s="9"/>
+    </row>
+    <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9"/>
+      <c r="G94" s="9"/>
+      <c r="H94" s="9"/>
+      <c r="I94" s="9"/>
+      <c r="J94" s="9"/>
+      <c r="K94" s="9"/>
+      <c r="L94" s="9"/>
+      <c r="M94" s="9"/>
+    </row>
+    <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="9"/>
+      <c r="I95" s="9"/>
+      <c r="J95" s="9"/>
+      <c r="K95" s="9"/>
+      <c r="L95" s="9"/>
+      <c r="M95" s="9"/>
+    </row>
+    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B93" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="8"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="M93" s="8"/>
-    </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="8" t="s">
+      <c r="B96" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9"/>
+      <c r="G96" s="9"/>
+      <c r="H96" s="9"/>
+      <c r="I96" s="9"/>
+      <c r="J96" s="9"/>
+      <c r="K96" s="9"/>
+      <c r="L96" s="9"/>
+      <c r="M96" s="9"/>
+    </row>
+    <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9"/>
+      <c r="G97" s="9"/>
+      <c r="H97" s="9"/>
+      <c r="I97" s="9"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="9"/>
+      <c r="L97" s="9"/>
+      <c r="M97" s="9"/>
+    </row>
+    <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="8"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="M94" s="8"/>
-    </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="8" t="s">
+      <c r="B98" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9"/>
+      <c r="G98" s="9"/>
+      <c r="H98" s="9"/>
+      <c r="I98" s="9"/>
+      <c r="J98" s="9"/>
+      <c r="K98" s="9"/>
+      <c r="L98" s="9"/>
+      <c r="M98" s="9"/>
+    </row>
+    <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B95" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="8"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="M95" s="8"/>
-    </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="8" t="s">
+      <c r="B99" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
+      <c r="I99" s="9"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="9"/>
+      <c r="L99" s="9"/>
+      <c r="M99" s="9"/>
+    </row>
+    <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C100" s="9"/>
+      <c r="D100" s="9"/>
+      <c r="E100" s="9"/>
+      <c r="F100" s="9"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="9"/>
+      <c r="I100" s="9"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="9"/>
+      <c r="L100" s="9"/>
+      <c r="M100" s="9"/>
+    </row>
+    <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B96" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="8"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="M96" s="8"/>
-    </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="8" t="s">
+      <c r="B101" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C101" s="9"/>
+      <c r="D101" s="9"/>
+      <c r="E101" s="9"/>
+      <c r="F101" s="9"/>
+      <c r="G101" s="9"/>
+      <c r="H101" s="9"/>
+      <c r="I101" s="9"/>
+      <c r="J101" s="9"/>
+      <c r="K101" s="9"/>
+      <c r="L101" s="9"/>
+      <c r="M101" s="9"/>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-    </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="8"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="M98" s="8"/>
-    </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B99" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-    </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="M100" s="8"/>
-    </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="8"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="M101" s="8"/>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
-      <c r="E102" s="6"/>
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6"/>
-      <c r="L102" s="6"/>
-      <c r="M102" s="6"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="7"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7"/>
+      <c r="M102" s="7"/>
     </row>
     <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/tests/fixtures/22_weekly_timesheet/22_weekly_timesheet_pattern-manual.xlsx
+++ b/tests/fixtures/22_weekly_timesheet/22_weekly_timesheet_pattern-manual.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="115">
   <si>
     <t xml:space="preserve">config:</t>
   </si>
@@ -118,142 +118,36 @@
     <t xml:space="preserve">Regular.*</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">col_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">header_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">overtime</t>
-    </r>
+    <t xml:space="preserve">col_header_overtime</t>
   </si>
   <si>
     <t xml:space="preserve">Overtime.*</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">col_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">header_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">sick</t>
-    </r>
+    <t xml:space="preserve">col_header_sick</t>
   </si>
   <si>
     <t xml:space="preserve">Sick.*</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">col_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">header_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">holiday</t>
-    </r>
+    <t xml:space="preserve">col_header_holiday</t>
   </si>
   <si>
     <t xml:space="preserve">Holiday.*</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">col_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">header_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">vacation</t>
-    </r>
+    <t xml:space="preserve">col_header_vacation</t>
   </si>
   <si>
     <t xml:space="preserve">Vacation.*</t>
   </si>
   <si>
+    <t xml:space="preserve">greand_total_lbl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand total.*</t>
+  </si>
+  <si>
     <t xml:space="preserve">var:not-null</t>
   </si>
   <si>
@@ -362,196 +256,34 @@
     <t xml:space="preserve">currency</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rate.overtime</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rate.sick</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rate.holiday</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">rate.vacation</t>
-    </r>
+    <t xml:space="preserve">employee.rate.overtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.rate.sick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.rate.holiday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.rate.vacation</t>
   </si>
   <si>
     <t xml:space="preserve">employee.pay.regular</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pay.overtime</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pay.sick</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pay.holiday</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pay.vacation</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">employee.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">pay.grand_total</t>
-    </r>
+    <t xml:space="preserve">employee.pay.overtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.pay.sick</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.pay.holiday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.pay.vacation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">employee.pay.grand_total</t>
   </si>
   <si>
     <t xml:space="preserve">START:</t>
@@ -584,13 +316,13 @@
     <t xml:space="preserve">read employee data</t>
   </si>
   <si>
-    <t xml:space="preserve">seek:g4</t>
-  </si>
-  <si>
     <t xml:space="preserve">dir:LR</t>
   </si>
   <si>
-    <t xml:space="preserve">seek:a8</t>
+    <t xml:space="preserve">cell:g4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell:next</t>
   </si>
   <si>
     <t xml:space="preserve">table:2</t>
@@ -614,10 +346,7 @@
     <t xml:space="preserve">FOOTER:1</t>
   </si>
   <si>
-    <t xml:space="preserve">seek:g30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cell:next</t>
+    <t xml:space="preserve">cell:h30</t>
   </si>
   <si>
     <t xml:space="preserve">cell:H31</t>
@@ -627,6 +356,9 @@
   </si>
   <si>
     <t xml:space="preserve">CeLL:1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cell:g33</t>
   </si>
   <si>
     <t xml:space="preserve">cElL:next</t>
@@ -642,7 +374,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -664,12 +396,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -762,7 +488,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -784,10 +510,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1131,6 +853,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3" t="b">
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D3" s="2"/>
@@ -1387,7 +1110,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>12</v>
       </c>
@@ -1410,7 +1133,7 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -1433,7 +1156,7 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
     </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>12</v>
       </c>
@@ -1549,10 +1272,18 @@
       <c r="M22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
+      <c r="A23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -1565,16 +1296,16 @@
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -1588,16 +1319,16 @@
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -1611,16 +1342,16 @@
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -1634,16 +1365,16 @@
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -1657,16 +1388,16 @@
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -1680,16 +1411,16 @@
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -1703,16 +1434,16 @@
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -1726,13 +1457,13 @@
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -1747,13 +1478,13 @@
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
@@ -1768,13 +1499,13 @@
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
@@ -1789,13 +1520,13 @@
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -1810,13 +1541,13 @@
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -1831,13 +1562,13 @@
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -1852,13 +1583,13 @@
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -1873,13 +1604,13 @@
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -1894,13 +1625,13 @@
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -1915,13 +1646,13 @@
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -1936,13 +1667,13 @@
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
@@ -1957,13 +1688,13 @@
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
@@ -1978,13 +1709,13 @@
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
@@ -1999,13 +1730,13 @@
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -2020,13 +1751,13 @@
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
@@ -2041,13 +1772,13 @@
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
@@ -2062,13 +1793,13 @@
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
@@ -2083,13 +1814,13 @@
     </row>
     <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>78</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
@@ -2104,13 +1835,13 @@
     </row>
     <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B50" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5"/>
@@ -2125,13 +1856,13 @@
     </row>
     <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>78</v>
+        <v>57</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
@@ -2146,13 +1877,13 @@
     </row>
     <row r="52" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>79</v>
+        <v>57</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
@@ -2167,13 +1898,13 @@
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
@@ -2188,13 +1919,13 @@
     </row>
     <row r="54" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>81</v>
+        <v>57</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
@@ -2209,13 +1940,13 @@
     </row>
     <row r="55" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>82</v>
+        <v>57</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2230,13 +1961,13 @@
     </row>
     <row r="56" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>83</v>
+        <v>57</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>85</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
@@ -2251,13 +1982,13 @@
     </row>
     <row r="57" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>84</v>
+        <v>57</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
@@ -2272,13 +2003,13 @@
     </row>
     <row r="58" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>85</v>
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -2292,417 +2023,413 @@
       <c r="M58" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="7"/>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
+      <c r="A60" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8"/>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
-      <c r="M61" s="8"/>
+      <c r="A61" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
+      <c r="H61" s="7"/>
+      <c r="I61" s="7"/>
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+      <c r="L61" s="7"/>
+      <c r="M61" s="7"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="M62" s="8"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="M63" s="8"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="9"/>
-      <c r="D62" s="9"/>
-      <c r="E62" s="9"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9"/>
-      <c r="J62" s="9"/>
-      <c r="K62" s="9"/>
-      <c r="L62" s="9"/>
-      <c r="M62" s="9"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C63" s="9"/>
-      <c r="D63" s="9"/>
-      <c r="E63" s="9"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="9"/>
-      <c r="I63" s="9"/>
-      <c r="J63" s="9"/>
-      <c r="K63" s="9"/>
-      <c r="L63" s="9"/>
-      <c r="M63" s="9"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="8"/>
+      <c r="B64" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="7"/>
+      <c r="H64" s="7"/>
+      <c r="I64" s="7"/>
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
+      <c r="L64" s="7"/>
+      <c r="M64" s="7"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="9"/>
-      <c r="M65" s="9"/>
+      <c r="A65" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="M65" s="8"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C66" s="9"/>
-      <c r="D66" s="9"/>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
-      <c r="K66" s="9"/>
-      <c r="L66" s="9"/>
-      <c r="M66" s="9"/>
+      <c r="A66" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="M66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
-      <c r="K67" s="9"/>
-      <c r="L67" s="9"/>
-      <c r="M67" s="9"/>
+      <c r="A67" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="M67" s="8"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C68" s="9"/>
-      <c r="D68" s="9"/>
-      <c r="E68" s="9"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
-      <c r="K68" s="9"/>
-      <c r="L68" s="9"/>
-      <c r="M68" s="9"/>
+      <c r="A68" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="M68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
-      <c r="I69" s="9"/>
-      <c r="J69" s="9"/>
-      <c r="K69" s="9"/>
-      <c r="L69" s="9"/>
-      <c r="M69" s="9"/>
+      <c r="A69" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="M69" s="8"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8"/>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
+      <c r="A70" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="7"/>
+      <c r="I70" s="7"/>
+      <c r="J70" s="7"/>
+      <c r="K70" s="7"/>
+      <c r="L70" s="7"/>
+      <c r="M70" s="7"/>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
-      <c r="E71" s="9"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="9"/>
-      <c r="I71" s="9"/>
-      <c r="J71" s="9"/>
-      <c r="K71" s="9"/>
-      <c r="L71" s="9"/>
-      <c r="M71" s="9"/>
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="M71" s="8"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="B72" s="9"/>
-      <c r="C72" s="9"/>
-      <c r="D72" s="9"/>
-      <c r="E72" s="9"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
-      <c r="I72" s="9"/>
-      <c r="J72" s="9"/>
-      <c r="K72" s="9"/>
-      <c r="L72" s="9"/>
-      <c r="M72" s="9"/>
+      <c r="A72" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="M72" s="8"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="9" t="s">
-        <v>94</v>
+      <c r="A73" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C73" s="9"/>
-      <c r="D73" s="9"/>
-      <c r="E73" s="9"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="9"/>
-      <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
-      <c r="M73" s="9"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="8"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="M73" s="8"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
-      <c r="E74" s="9"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
-      <c r="M74" s="9"/>
+      <c r="A74" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="8"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="M74" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="9" t="s">
-        <v>94</v>
+      <c r="A75" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="B75" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
-      <c r="E75" s="9"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-      <c r="J75" s="9"/>
-      <c r="K75" s="9"/>
-      <c r="L75" s="9"/>
-      <c r="M75" s="9"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="M75" s="8"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C76" s="9"/>
-      <c r="D76" s="9"/>
-      <c r="E76" s="9"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="9"/>
-      <c r="H76" s="9"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="9"/>
-      <c r="K76" s="9"/>
-      <c r="L76" s="9"/>
-      <c r="M76" s="9"/>
+      <c r="A76" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+      <c r="M76" s="8"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="9" t="s">
-        <v>94</v>
+      <c r="A77" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C77" s="9"/>
-      <c r="D77" s="9"/>
-      <c r="E77" s="9"/>
-      <c r="F77" s="9"/>
-      <c r="G77" s="9"/>
-      <c r="H77" s="9"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="9"/>
-      <c r="K77" s="9"/>
-      <c r="L77" s="9"/>
-      <c r="M77" s="9"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+      <c r="M77" s="8"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" s="9"/>
-      <c r="D78" s="9"/>
-      <c r="E78" s="9"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
-      <c r="K78" s="9"/>
-      <c r="L78" s="9"/>
-      <c r="M78" s="9"/>
+      <c r="A78" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+      <c r="M78" s="8"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B79" s="9"/>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="9"/>
-      <c r="H79" s="9"/>
-      <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
-      <c r="K79" s="9"/>
-      <c r="L79" s="9"/>
-      <c r="M79" s="9"/>
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+      <c r="M79" s="8"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B80" s="10"/>
-      <c r="C80" s="10"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-      <c r="J80" s="10"/>
-      <c r="K80" s="10"/>
-      <c r="L80" s="10"/>
-      <c r="M80" s="10"/>
+      <c r="A80" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="9"/>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
+      <c r="G80" s="9"/>
+      <c r="H80" s="9"/>
+      <c r="I80" s="9"/>
+      <c r="J80" s="9"/>
+      <c r="K80" s="9"/>
+      <c r="L80" s="9"/>
+      <c r="M80" s="9"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="10"/>
-      <c r="B81" s="10" t="s">
+      <c r="A81" s="9"/>
+      <c r="B81" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="10"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
-      <c r="J81" s="10"/>
-      <c r="K81" s="10"/>
-      <c r="L81" s="10"/>
-      <c r="M81" s="10"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
+      <c r="M81" s="9"/>
     </row>
     <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>22</v>
@@ -2717,7 +2444,7 @@
         <v>24</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>28</v>
@@ -2739,366 +2466,382 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C83" s="11" t="s">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D83" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="D83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="F83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="H83" s="11" t="s">
+      <c r="E83" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="K83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="L83" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="M83" s="11" t="s">
-        <v>101</v>
+      <c r="F83" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="J83" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="K83" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="L83" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="M83" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L84" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M84" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
       <c r="B85" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>28</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="9"/>
-      <c r="D90" s="9"/>
-      <c r="E90" s="9"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
-      <c r="I90" s="9"/>
-      <c r="J90" s="9"/>
-      <c r="K90" s="9"/>
-      <c r="L90" s="9"/>
-      <c r="M90" s="9"/>
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="9" t="s">
-        <v>107</v>
+      <c r="A91" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C91" s="9"/>
-      <c r="D91" s="9"/>
-      <c r="E91" s="9"/>
-      <c r="F91" s="9"/>
-      <c r="G91" s="9"/>
-      <c r="H91" s="9"/>
-      <c r="I91" s="9"/>
-      <c r="J91" s="9"/>
-      <c r="K91" s="9"/>
-      <c r="L91" s="9"/>
-      <c r="M91" s="9"/>
+        <v>76</v>
+      </c>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
     </row>
     <row r="92" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C92" s="9"/>
-      <c r="D92" s="9"/>
-      <c r="E92" s="9"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="9"/>
-      <c r="H92" s="9"/>
-      <c r="I92" s="9"/>
-      <c r="J92" s="9"/>
-      <c r="K92" s="9"/>
-      <c r="L92" s="9"/>
-      <c r="M92" s="9"/>
+      <c r="A92" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="M92" s="8"/>
     </row>
     <row r="93" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C93" s="9"/>
-      <c r="D93" s="9"/>
-      <c r="E93" s="9"/>
-      <c r="F93" s="9"/>
-      <c r="G93" s="9"/>
-      <c r="H93" s="9"/>
-      <c r="I93" s="9"/>
-      <c r="J93" s="9"/>
-      <c r="K93" s="9"/>
-      <c r="L93" s="9"/>
-      <c r="M93" s="9"/>
+      <c r="A93" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="M93" s="8"/>
     </row>
     <row r="94" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C94" s="9"/>
-      <c r="D94" s="9"/>
-      <c r="E94" s="9"/>
-      <c r="F94" s="9"/>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
-      <c r="I94" s="9"/>
-      <c r="J94" s="9"/>
-      <c r="K94" s="9"/>
-      <c r="L94" s="9"/>
-      <c r="M94" s="9"/>
+      <c r="A94" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="M94" s="8"/>
     </row>
     <row r="95" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C95" s="9"/>
-      <c r="D95" s="9"/>
-      <c r="E95" s="9"/>
-      <c r="F95" s="9"/>
-      <c r="G95" s="9"/>
-      <c r="H95" s="9"/>
-      <c r="I95" s="9"/>
-      <c r="J95" s="9"/>
-      <c r="K95" s="9"/>
-      <c r="L95" s="9"/>
-      <c r="M95" s="9"/>
+      <c r="A95" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="M95" s="8"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="9" t="s">
-        <v>108</v>
+      <c r="A96" s="8" t="s">
+        <v>109</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C96" s="9"/>
-      <c r="D96" s="9"/>
-      <c r="E96" s="9"/>
-      <c r="F96" s="9"/>
-      <c r="G96" s="9"/>
-      <c r="H96" s="9"/>
-      <c r="I96" s="9"/>
-      <c r="J96" s="9"/>
-      <c r="K96" s="9"/>
-      <c r="L96" s="9"/>
-      <c r="M96" s="9"/>
+        <v>82</v>
+      </c>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="M96" s="8"/>
     </row>
     <row r="97" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C97" s="9"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="9"/>
-      <c r="F97" s="9"/>
-      <c r="G97" s="9"/>
-      <c r="H97" s="9"/>
-      <c r="I97" s="9"/>
-      <c r="J97" s="9"/>
-      <c r="K97" s="9"/>
-      <c r="L97" s="9"/>
-      <c r="M97" s="9"/>
+      <c r="A97" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
     </row>
     <row r="98" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C98" s="9"/>
-      <c r="D98" s="9"/>
-      <c r="E98" s="9"/>
-      <c r="F98" s="9"/>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
-      <c r="I98" s="9"/>
-      <c r="J98" s="9"/>
-      <c r="K98" s="9"/>
-      <c r="L98" s="9"/>
-      <c r="M98" s="9"/>
+      <c r="A98" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="M98" s="8"/>
     </row>
     <row r="99" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C99" s="9"/>
-      <c r="D99" s="9"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-      <c r="J99" s="9"/>
-      <c r="K99" s="9"/>
-      <c r="L99" s="9"/>
-      <c r="M99" s="9"/>
+      <c r="A99" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
     </row>
     <row r="100" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C100" s="9"/>
-      <c r="D100" s="9"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="9"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="9"/>
-      <c r="I100" s="9"/>
-      <c r="J100" s="9"/>
-      <c r="K100" s="9"/>
-      <c r="L100" s="9"/>
-      <c r="M100" s="9"/>
-    </row>
-    <row r="101" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="9" t="s">
+      <c r="A100" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B101" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C101" s="9"/>
-      <c r="D101" s="9"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="9"/>
-      <c r="G101" s="9"/>
-      <c r="H101" s="9"/>
-      <c r="I101" s="9"/>
-      <c r="J101" s="9"/>
-      <c r="K101" s="9"/>
-      <c r="L101" s="9"/>
-      <c r="M101" s="9"/>
-    </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="7" t="s">
+      <c r="B100" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="M100" s="8"/>
+    </row>
+    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B102" s="7"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="7"/>
-      <c r="F102" s="7"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7"/>
-      <c r="I102" s="7"/>
-      <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
-      <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
-    </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B101" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+    </row>
+    <row r="102" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="M102" s="8"/>
+    </row>
+    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+    </row>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
